--- a/extracted_cycles.xlsx
+++ b/extracted_cycles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>57913344</t>
+          <t>435.24</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>115605504</t>
+          <t>2095.84</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>220889088</t>
+          <t>2238.17</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57913344</t>
+          <t>2873.61</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>115605504</t>
+          <t>3050.62</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>248062464</t>
+          <t>2973.78</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>14635008</t>
+          <t>3640.80</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>47759360</t>
+          <t>4050.30</t>
         </is>
       </c>
     </row>
@@ -594,143 +594,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>156514012</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>layer-9</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>expand-0.1</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>79011840</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>layer-10</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>expand-0.1</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>47759360</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>layer-11</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>expand-0.1</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>156514012</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>layer-12</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>expand-0.1</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>79011840</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>layer-13</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>expand-0.1</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>47759360</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>layer-14</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>expand-0.1</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>156514012</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>layer-15</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>expand-0.1</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>91914240</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>layer-16</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>expand-0.1</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>84541440</t>
+          <t>4067.50</t>
         </is>
       </c>
     </row>

--- a/extracted_cycles.xlsx
+++ b/extracted_cycles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,12 +453,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>435.24</t>
+          <t>101711873</t>
         </is>
       </c>
     </row>
@@ -470,12 +470,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2095.84</t>
+          <t>8388608</t>
         </is>
       </c>
     </row>
@@ -487,12 +487,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2238.17</t>
+          <t>12582912</t>
         </is>
       </c>
     </row>
@@ -504,12 +504,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2873.61</t>
+          <t>34603008</t>
         </is>
       </c>
     </row>
@@ -521,12 +521,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3050.62</t>
+          <t>135266304</t>
         </is>
       </c>
     </row>
@@ -538,63 +538,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2973.78</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>layer-6</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>expand-0.1</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>3640.80</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>layer-7</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>expand-0.1</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>4050.30</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>layer-8</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>expand-0.1</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>4067.50</t>
+          <t>138412032</t>
         </is>
       </c>
     </row>

--- a/extracted_cycles.xlsx
+++ b/extracted_cycles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,12 +453,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>101711873</t>
+          <t>450800</t>
         </is>
       </c>
     </row>
@@ -470,12 +470,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>8388608</t>
+          <t>901600</t>
         </is>
       </c>
     </row>
@@ -487,12 +487,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>12582912</t>
+          <t>1803200</t>
         </is>
       </c>
     </row>
@@ -504,12 +504,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>34603008</t>
+          <t>1346950</t>
         </is>
       </c>
     </row>
@@ -521,12 +521,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>135266304</t>
+          <t>2808000</t>
         </is>
       </c>
     </row>
@@ -538,12 +538,1202 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>138412032</t>
+          <t>5451000</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>layer-6</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>46080</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>layer-7</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>27648</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>layer-8</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>25920</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>layer-9</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>25920</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>layer-10</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>93312</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>layer-11</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>104976</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>layer-12</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>124416</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>layer-13</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>56448</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>layer-14</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>158272</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>layer-15</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>401408</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>layer-16</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1204224</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>layer-17</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>903168</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>layer-18</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1032192</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>layer-19</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>516096</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>layer-20</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>317824</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>layer-21</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>802816</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>layer-22</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1806336</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>layer-23</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1806336</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>layer-24</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1827504</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>layer-25</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>903168</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>layer-26</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>365568</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>layer-27</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>526848</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>layer-28</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>134400</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>layer-29</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>20352</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>layer-30</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>134400</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>layer-31</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>24832</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>layer-32</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>31720</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>layer-33</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>356312</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>layer-34</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1053696</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>layer-35</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>235200</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>layer-36</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>39168</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>layer-37</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>260872</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>layer-38</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>37632</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>layer-39</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>36816</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>layer-40</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>456272</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>layer-41</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>24160</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>layer-42</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>127008</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>layer-43</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>100352</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>layer-44</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>112896</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>layer-45</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>50176</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>layer-46</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>14464</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>layer-47</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>143616</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>layer-48</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>56756</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>layer-49</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>35904</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>layer-50</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>158488</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>layer-51</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>225792</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>layer-52</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>200704</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>layer-53</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>225792</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>layer-54</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>100352</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>layer-55</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>25088</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>layer-56</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>225792</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>layer-57</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>100352</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>layer-58</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>39040</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>layer-59</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>181248</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>layer-60</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>901600</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>layer-61</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>1008000</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>layer-62</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>5632000</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>layer-63</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>1098240</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>layer-64</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>5600000</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>layer-65</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>967680</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>layer-66</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>5698000</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>layer-67</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>967680</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>layer-68</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>1803200</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>layer-69</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2016000</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>layer-70</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>11200000</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>layer-71</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2016000</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>layer-72</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>11440000</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>layer-73</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>1935360</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>layer-74</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>14447360</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>layer-75</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>expand-0.1</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2067120</t>
         </is>
       </c>
     </row>

--- a/extracted_cycles.xlsx
+++ b/extracted_cycles.xlsx
@@ -453,12 +453,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>450800</t>
+          <t>8.22e+03</t>
         </is>
       </c>
     </row>
@@ -470,12 +470,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>901600</t>
+          <t>2.65e+04</t>
         </is>
       </c>
     </row>
@@ -487,12 +487,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1803200</t>
+          <t>1.11e+05</t>
         </is>
       </c>
     </row>
@@ -504,12 +504,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1346950</t>
+          <t>6.58e+04</t>
         </is>
       </c>
     </row>
@@ -521,12 +521,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2808000</t>
+          <t>2.22e+05</t>
         </is>
       </c>
     </row>
@@ -538,12 +538,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>5451000</t>
+          <t>4.61e+05</t>
         </is>
       </c>
     </row>
@@ -555,12 +555,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>46080</t>
+          <t>3.83e+01</t>
         </is>
       </c>
     </row>
@@ -572,12 +572,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>27648</t>
+          <t>7.80e+01</t>
         </is>
       </c>
     </row>
@@ -589,12 +589,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>25920</t>
+          <t>4.39e+01</t>
         </is>
       </c>
     </row>
@@ -606,12 +606,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>25920</t>
+          <t>2.98e+01</t>
         </is>
       </c>
     </row>
@@ -623,12 +623,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>93312</t>
+          <t>3.06e+02</t>
         </is>
       </c>
     </row>
@@ -640,12 +640,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>104976</t>
+          <t>4.56e+02</t>
         </is>
       </c>
     </row>
@@ -657,12 +657,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>124416</t>
+          <t>1.47e+02</t>
         </is>
       </c>
     </row>
@@ -674,12 +674,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>56448</t>
+          <t>1.42e+02</t>
         </is>
       </c>
     </row>
@@ -691,12 +691,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>158272</t>
+          <t>6.09e+02</t>
         </is>
       </c>
     </row>
@@ -708,12 +708,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>401408</t>
+          <t>4.88e+03</t>
         </is>
       </c>
     </row>
@@ -725,12 +725,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1204224</t>
+          <t>5.49e+04</t>
         </is>
       </c>
     </row>
@@ -742,12 +742,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>903168</t>
+          <t>1.70e+04</t>
         </is>
       </c>
     </row>
@@ -759,12 +759,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1032192</t>
+          <t>1.46e+04</t>
         </is>
       </c>
     </row>
@@ -776,12 +776,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>516096</t>
+          <t>7.33e+03</t>
         </is>
       </c>
     </row>
@@ -793,12 +793,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>317824</t>
+          <t>2.06e+03</t>
         </is>
       </c>
     </row>
@@ -810,12 +810,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>802816</t>
+          <t>1.80e+04</t>
         </is>
       </c>
     </row>
@@ -827,12 +827,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1806336</t>
+          <t>2.07e+05</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1806336</t>
+          <t>1.30e+05</t>
         </is>
       </c>
     </row>
@@ -861,12 +861,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1827504</t>
+          <t>1.40e+05</t>
         </is>
       </c>
     </row>
@@ -878,12 +878,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>903168</t>
+          <t>3.61e+04</t>
         </is>
       </c>
     </row>
@@ -895,12 +895,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>365568</t>
+          <t>3.96e+03</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>526848</t>
+          <t>1.85e+04</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>134400</t>
+          <t>6.84e+02</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>20352</t>
+          <t>9.42e+00</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>134400</t>
+          <t>8.47e+02</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>24832</t>
+          <t>1.53e+01</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>31720</t>
+          <t>1.88e+01</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>356312</t>
+          <t>3.04e+03</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1053696</t>
+          <t>5.20e+05</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1048,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>235200</t>
+          <t>2.94e+03</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>39168</t>
+          <t>3.49e+01</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>260872</t>
+          <t>2.03e+03</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>37632</t>
+          <t>4.78e+01</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>36816</t>
+          <t>3.16e+01</t>
         </is>
       </c>
     </row>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>456272</t>
+          <t>6.77e+03</t>
         </is>
       </c>
     </row>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>24160</t>
+          <t>2.65e+02</t>
         </is>
       </c>
     </row>
@@ -1167,12 +1167,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>127008</t>
+          <t>2.20e+02</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>100352</t>
+          <t>3.24e+02</t>
         </is>
       </c>
     </row>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>112896</t>
+          <t>5.82e+02</t>
         </is>
       </c>
     </row>
@@ -1218,12 +1218,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>50176</t>
+          <t>1.14e+02</t>
         </is>
       </c>
     </row>
@@ -1235,12 +1235,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>14464</t>
+          <t>6.05e+00</t>
         </is>
       </c>
     </row>
@@ -1252,12 +1252,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>143616</t>
+          <t>4.21e+02</t>
         </is>
       </c>
     </row>
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>56756</t>
+          <t>1.94e+02</t>
         </is>
       </c>
     </row>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>35904</t>
+          <t>2.85e+01</t>
         </is>
       </c>
     </row>
@@ -1303,12 +1303,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>158488</t>
+          <t>6.74e+02</t>
         </is>
       </c>
     </row>
@@ -1320,12 +1320,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>225792</t>
+          <t>2.53e+03</t>
         </is>
       </c>
     </row>
@@ -1337,12 +1337,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>200704</t>
+          <t>1.38e+03</t>
         </is>
       </c>
     </row>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>225792</t>
+          <t>2.12e+03</t>
         </is>
       </c>
     </row>
@@ -1371,12 +1371,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>100352</t>
+          <t>4.54e+02</t>
         </is>
       </c>
     </row>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>25088</t>
+          <t>1.56e+01</t>
         </is>
       </c>
     </row>
@@ -1405,12 +1405,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>225792</t>
+          <t>3.30e+03</t>
         </is>
       </c>
     </row>
@@ -1422,12 +1422,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>100352</t>
+          <t>1.13e+03</t>
         </is>
       </c>
     </row>
@@ -1439,12 +1439,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>39040</t>
+          <t>5.02e+01</t>
         </is>
       </c>
     </row>
@@ -1456,12 +1456,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>181248</t>
+          <t>2.06e+03</t>
         </is>
       </c>
     </row>
@@ -1473,12 +1473,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>901600</t>
+          <t>2.40e+04</t>
         </is>
       </c>
     </row>
@@ -1490,12 +1490,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>1008000</t>
+          <t>1.28e+05</t>
         </is>
       </c>
     </row>
@@ -1507,12 +1507,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>5632000</t>
+          <t>1.42e+06</t>
         </is>
       </c>
     </row>
@@ -1524,12 +1524,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>1098240</t>
+          <t>4.21e+04</t>
         </is>
       </c>
     </row>
@@ -1541,12 +1541,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>5600000</t>
+          <t>2.31e+06</t>
         </is>
       </c>
     </row>
@@ -1558,12 +1558,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>967680</t>
+          <t>3.00e+04</t>
         </is>
       </c>
     </row>
@@ -1575,12 +1575,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>5698000</t>
+          <t>1.91e+06</t>
         </is>
       </c>
     </row>
@@ -1592,12 +1592,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>967680</t>
+          <t>4.09e+04</t>
         </is>
       </c>
     </row>
@@ -1609,12 +1609,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>1803200</t>
+          <t>8.75e+04</t>
         </is>
       </c>
     </row>
@@ -1626,12 +1626,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2016000</t>
+          <t>2.53e+05</t>
         </is>
       </c>
     </row>
@@ -1643,12 +1643,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>11200000</t>
+          <t>8.98e+06</t>
         </is>
       </c>
     </row>
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2016000</t>
+          <t>1.67e+05</t>
         </is>
       </c>
     </row>
@@ -1677,12 +1677,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>11440000</t>
+          <t>7.25e+06</t>
         </is>
       </c>
     </row>
@@ -1694,12 +1694,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>1935360</t>
+          <t>1.29e+05</t>
         </is>
       </c>
     </row>
@@ -1711,12 +1711,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>14447360</t>
+          <t>5.69e+06</t>
         </is>
       </c>
     </row>
@@ -1728,12 +1728,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>expand-0.1</t>
+          <t>expand-0.0</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2067120</t>
+          <t>1.47e+05</t>
         </is>
       </c>
     </row>

--- a/extracted_cycles.xlsx
+++ b/extracted_cycles.xlsx
@@ -453,12 +453,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.22e+03</t>
+          <t>3.32e+02</t>
         </is>
       </c>
     </row>
@@ -470,12 +470,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.65e+04</t>
+          <t>1.32e+03</t>
         </is>
       </c>
     </row>
@@ -487,12 +487,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.11e+05</t>
+          <t>5.23e+03</t>
         </is>
       </c>
     </row>
@@ -504,12 +504,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>6.58e+04</t>
+          <t>2.92e+03</t>
         </is>
       </c>
     </row>
@@ -521,12 +521,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.22e+05</t>
+          <t>9.15e+03</t>
         </is>
       </c>
     </row>
@@ -538,12 +538,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4.61e+05</t>
+          <t>3.96e+04</t>
         </is>
       </c>
     </row>
@@ -555,12 +555,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.83e+01</t>
+          <t>1.96e+00</t>
         </is>
       </c>
     </row>
@@ -572,12 +572,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>7.80e+01</t>
+          <t>1.54e+00</t>
         </is>
       </c>
     </row>
@@ -589,12 +589,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4.39e+01</t>
+          <t>1.15e+00</t>
         </is>
       </c>
     </row>
@@ -606,12 +606,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.98e+01</t>
+          <t>1.73e+00</t>
         </is>
       </c>
     </row>
@@ -623,12 +623,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3.06e+02</t>
+          <t>1.05e+01</t>
         </is>
       </c>
     </row>
@@ -640,12 +640,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4.56e+02</t>
+          <t>2.21e+01</t>
         </is>
       </c>
     </row>
@@ -657,12 +657,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.47e+02</t>
+          <t>1.90e+01</t>
         </is>
       </c>
     </row>
@@ -674,12 +674,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.42e+02</t>
+          <t>1.02e+01</t>
         </is>
       </c>
     </row>
@@ -691,12 +691,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>6.09e+02</t>
+          <t>3.23e+01</t>
         </is>
       </c>
     </row>
@@ -708,12 +708,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4.88e+03</t>
+          <t>1.71e+02</t>
         </is>
       </c>
     </row>
@@ -725,12 +725,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>5.49e+04</t>
+          <t>2.12e+03</t>
         </is>
       </c>
     </row>
@@ -742,12 +742,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.70e+04</t>
+          <t>1.41e+03</t>
         </is>
       </c>
     </row>
@@ -759,12 +759,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.46e+04</t>
+          <t>2.10e+03</t>
         </is>
       </c>
     </row>
@@ -776,12 +776,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>7.33e+03</t>
+          <t>8.94e+02</t>
         </is>
       </c>
     </row>
@@ -793,12 +793,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2.06e+03</t>
+          <t>1.79e+02</t>
         </is>
       </c>
     </row>
@@ -810,12 +810,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.80e+04</t>
+          <t>6.80e+02</t>
         </is>
       </c>
     </row>
@@ -827,12 +827,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2.07e+05</t>
+          <t>7.84e+03</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1.30e+05</t>
+          <t>5.16e+03</t>
         </is>
       </c>
     </row>
@@ -861,12 +861,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1.40e+05</t>
+          <t>7.66e+03</t>
         </is>
       </c>
     </row>
@@ -878,12 +878,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>3.61e+04</t>
+          <t>2.64e+03</t>
         </is>
       </c>
     </row>
@@ -895,12 +895,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>3.96e+03</t>
+          <t>2.64e+02</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1.85e+04</t>
+          <t>8.88e+02</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>6.84e+02</t>
+          <t>3.60e+01</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>9.42e+00</t>
+          <t>6.60e</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>8.47e+02</t>
+          <t>5.41e+01</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1.53e+01</t>
+          <t>1.66e+00</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1.88e+01</t>
+          <t>1.26e+00</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>3.04e+03</t>
+          <t>2.01e+02</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>5.20e+05</t>
+          <t>1.81e+03</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1048,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2.94e+03</t>
+          <t>1.12e+02</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>3.49e+01</t>
+          <t>2.49e+00</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2.03e+03</t>
+          <t>1.76e+02</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>4.78e+01</t>
+          <t>3.88e+00</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>3.16e+01</t>
+          <t>2.08e+00</t>
         </is>
       </c>
     </row>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>6.77e+03</t>
+          <t>4.45e+02</t>
         </is>
       </c>
     </row>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2.65e+02</t>
+          <t>1.37e+00</t>
         </is>
       </c>
     </row>
@@ -1167,12 +1167,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2.20e+02</t>
+          <t>2.22e+01</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>3.24e+02</t>
+          <t>1.78e+01</t>
         </is>
       </c>
     </row>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>5.82e+02</t>
+          <t>2.01e+01</t>
         </is>
       </c>
     </row>
@@ -1218,12 +1218,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1.14e+02</t>
+          <t>7.10e+00</t>
         </is>
       </c>
     </row>
@@ -1235,12 +1235,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>6.05e+00</t>
+          <t>5.21e</t>
         </is>
       </c>
     </row>
@@ -1252,12 +1252,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>4.21e+02</t>
+          <t>3.44e+01</t>
         </is>
       </c>
     </row>
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>1.94e+02</t>
+          <t>8.83e+00</t>
         </is>
       </c>
     </row>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2.85e+01</t>
+          <t>1.83e+00</t>
         </is>
       </c>
     </row>
@@ -1303,12 +1303,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>6.74e+02</t>
+          <t>4.21e+01</t>
         </is>
       </c>
     </row>
@@ -1320,12 +1320,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2.53e+03</t>
+          <t>1.29e+02</t>
         </is>
       </c>
     </row>
@@ -1337,12 +1337,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>1.38e+03</t>
+          <t>7.06e+01</t>
         </is>
       </c>
     </row>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2.12e+03</t>
+          <t>7.46e+01</t>
         </is>
       </c>
     </row>
@@ -1371,12 +1371,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>4.54e+02</t>
+          <t>2.68e+01</t>
         </is>
       </c>
     </row>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>1.56e+01</t>
+          <t>1.60e+00</t>
         </is>
       </c>
     </row>
@@ -1405,12 +1405,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>3.30e+03</t>
+          <t>1.24e+02</t>
         </is>
       </c>
     </row>
@@ -1422,12 +1422,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>1.13e+03</t>
+          <t>3.97e+01</t>
         </is>
       </c>
     </row>
@@ -1439,12 +1439,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>5.02e+01</t>
+          <t>3.84e+00</t>
         </is>
       </c>
     </row>
@@ -1456,12 +1456,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2.06e+03</t>
+          <t>6.93e+01</t>
         </is>
       </c>
     </row>
@@ -1473,12 +1473,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2.40e+04</t>
+          <t>8.56e+02</t>
         </is>
       </c>
     </row>
@@ -1490,12 +1490,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>1.28e+05</t>
+          <t>1.92e+03</t>
         </is>
       </c>
     </row>
@@ -1507,12 +1507,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>1.42e+06</t>
+          <t>4.32e+04</t>
         </is>
       </c>
     </row>
@@ -1524,12 +1524,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>4.21e+04</t>
+          <t>2.70e+03</t>
         </is>
       </c>
     </row>
@@ -1541,12 +1541,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2.31e+06</t>
+          <t>9.33e+04</t>
         </is>
       </c>
     </row>
@@ -1558,12 +1558,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>3.00e+04</t>
+          <t>2.12e+03</t>
         </is>
       </c>
     </row>
@@ -1575,12 +1575,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>1.91e+06</t>
+          <t>6.63e+04</t>
         </is>
       </c>
     </row>
@@ -1592,12 +1592,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>4.09e+04</t>
+          <t>2.51e+03</t>
         </is>
       </c>
     </row>
@@ -1609,12 +1609,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>8.75e+04</t>
+          <t>3.42e+03</t>
         </is>
       </c>
     </row>
@@ -1626,12 +1626,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2.53e+05</t>
+          <t>6.04e+03</t>
         </is>
       </c>
     </row>
@@ -1643,12 +1643,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>8.98e+06</t>
+          <t>4.99e+05</t>
         </is>
       </c>
     </row>
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>1.67e+05</t>
+          <t>5.11e+03</t>
         </is>
       </c>
     </row>
@@ -1677,12 +1677,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>7.25e+06</t>
+          <t>2.86e+05</t>
         </is>
       </c>
     </row>
@@ -1694,12 +1694,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>1.29e+05</t>
+          <t>7.20e+03</t>
         </is>
       </c>
     </row>
@@ -1711,12 +1711,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>5.69e+06</t>
+          <t>3.23e+05</t>
         </is>
       </c>
     </row>
@@ -1728,12 +1728,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>expand-0.0</t>
+          <t>expand-0.1</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>1.47e+05</t>
+          <t>8.64e+03</t>
         </is>
       </c>
     </row>

--- a/extracted_cycles.xlsx
+++ b/extracted_cycles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5.47e+02</t>
+          <t>4.18e+03</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>6.11e+01</t>
+          <t>4.18e+04</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4.27e+02</t>
+          <t>9.58e+03</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.75e+02</t>
+          <t>7.31e+04</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4.88e+02</t>
+          <t>1.32e+04</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.04e+03</t>
+          <t>1.19e+04</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5.67e+02</t>
+          <t>1.20e+04</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.82e+02</t>
+          <t>3.53e+04</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4.55e+02</t>
+          <t>3.10e+04</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2.18e+02</t>
+          <t>4.34e+04</t>
         </is>
       </c>
     </row>
@@ -568,7 +568,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2.27e+02</t>
+          <t>1.15e+04</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5.41e+02</t>
+          <t>1.42e+04</t>
         </is>
       </c>
     </row>
@@ -592,7 +592,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4.48e+02</t>
+          <t>1.66e+04</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1.78e+02</t>
+          <t>2.46e+06</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>6.28e+02</t>
+          <t>6.25e+04</t>
         </is>
       </c>
     </row>
@@ -628,103 +628,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1.14e+02</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>layer-16</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>5.58e+02</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>layer-17</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>3.16e+02</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>layer-18</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2.19e+03</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>layer-19</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>4.32e+02</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>layer-20</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2.56e+03</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>layer-21</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>4.37e+02</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>layer-22</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>3.55e+03</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>layer-23</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>9.25e+02</t>
+          <t>3.88e+03</t>
         </is>
       </c>
     </row>
